--- a/towers/FPR/DS Provide Decision Support/DS-020/input/data/R1_FutureFlows.xlsx
+++ b/towers/FPR/DS Provide Decision Support/DS-020/input/data/R1_FutureFlows.xlsx
@@ -878,112 +878,112 @@
       </c>
       <c r="Z2" s="6" t="inlineStr">
         <is>
-          <t>e.g. Cost Element</t>
+          <t>Business Data</t>
         </is>
       </c>
       <c r="AA2" s="6" t="inlineStr">
         <is>
-          <t>e.g. CSV / IDoc / JSON</t>
+          <t>JSON / CSV</t>
         </is>
       </c>
       <c r="AB2" s="6" t="inlineStr">
         <is>
-          <t>e.g. Intel Confidential</t>
+          <t>Intel Confidential</t>
         </is>
       </c>
       <c r="AC2" s="6" t="inlineStr">
         <is>
-          <t>e.g. 10K rows/day</t>
+          <t>~10K events/hour</t>
         </is>
       </c>
       <c r="AD2" s="6" t="inlineStr">
         <is>
-          <t>Master / Transaction</t>
+          <t>Transaction</t>
         </is>
       </c>
       <c r="AE2" s="6" t="inlineStr">
         <is>
-          <t>Lineage notes</t>
+          <t>e.g. MES 300 → e.g. XEUS: What data moves</t>
         </is>
       </c>
       <c r="AF2" s="6" t="inlineStr">
         <is>
-          <t>e.g. Pub-Sub / P2P / ETL</t>
+          <t>Point-to-Point</t>
         </is>
       </c>
       <c r="AG2" s="6" t="inlineStr">
         <is>
-          <t>e.g. Azure Service Bus</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="AH2" s="6" t="inlineStr">
         <is>
-          <t>e.g. REST / RFC / SFTP</t>
+          <t>REST / File</t>
         </is>
       </c>
       <c r="AI2" s="6" t="inlineStr">
         <is>
-          <t>e.g. OAuth / NTLM / Cert</t>
+          <t>Kerberos / X.509</t>
         </is>
       </c>
       <c r="AJ2" s="6" t="inlineStr">
         <is>
-          <t>DEV,QAS,PRD</t>
+          <t>DEV, QAS, PRD</t>
         </is>
       </c>
       <c r="AK2" s="6" t="inlineStr">
         <is>
-          <t>e.g. &lt; 5 min</t>
+          <t>&lt; 1 second (real-time)</t>
         </is>
       </c>
       <c r="AL2" s="6" t="inlineStr">
         <is>
-          <t>e.g. IF-DS020-001</t>
+          <t>IF-e.g.MESRou-01</t>
         </is>
       </c>
       <c r="AM2" s="6" t="inlineStr">
         <is>
-          <t>e.g. Inbound / Outbound</t>
+          <t>Point-to-Point</t>
         </is>
       </c>
       <c r="AN2" s="6" t="inlineStr">
         <is>
-          <t>e.g. Dead-letter queue</t>
+          <t>Retry 3x → Dead Letter Queue → Alert</t>
         </is>
       </c>
       <c r="AO2" s="6" t="inlineStr">
         <is>
-          <t>e.g. Splunk / AppDynamics</t>
+          <t>SAP CCMS / Azure Monitor / Splunk</t>
         </is>
       </c>
       <c r="AP2" s="6" t="inlineStr">
         <is>
-          <t>e.g. SAP HANA</t>
+          <t>Oracle DB</t>
         </is>
       </c>
       <c r="AQ2" s="6" t="inlineStr">
         <is>
-          <t>e.g. Azure SQL</t>
+          <t>Oracle DB</t>
         </is>
       </c>
       <c r="AR2" s="6" t="inlineStr">
         <is>
-          <t>e.g. CKMLHD table</t>
+          <t>MES300_PROD.What_data_moves</t>
         </is>
       </c>
       <c r="AS2" s="6" t="inlineStr">
         <is>
-          <t>e.g. dbo.CostElements</t>
+          <t>XEUS_PROD.What_data_moves</t>
         </is>
       </c>
       <c r="AT2" s="6" t="inlineStr">
         <is>
-          <t>e.g. S/4 HANA 2023</t>
+          <t>Intel MES On-Premise</t>
         </is>
       </c>
       <c r="AU2" s="6" t="inlineStr">
         <is>
-          <t>e.g. Azure PaaS</t>
+          <t>Intel Middleware On-Premise</t>
         </is>
       </c>
     </row>
